--- a/Excel/Lab 1/Lab 1 Solution.xlsx
+++ b/Excel/Lab 1/Lab 1 Solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB7BFDA-F1C1-4399-9078-9B4D0583A114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42492B40-FB1E-4684-B228-DAED6A022B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23760" windowHeight="15840" xr2:uid="{6E0772BF-1D0C-417B-A4B2-B12690A11A9F}"/>
   </bookViews>
@@ -48,30 +48,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -266,9 +244,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="[$EGP]\ #,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -651,7 +630,6 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -758,6 +736,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -773,13 +760,7 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -790,7 +771,38 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{38AF7B54-7C91-4C1A-A730-67FD4A2324F8}"/>
     <cellStyle name="عادي 2" xfId="3" xr:uid="{558F22E9-9660-430D-A588-08C9DFFD9DBD}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -814,9 +826,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>226867</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>8659</xdr:rowOff>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -831,8 +843,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5079422" y="2286001"/>
-          <a:ext cx="5348720" cy="1408833"/>
+          <a:off x="4965122" y="2286001"/>
+          <a:ext cx="5941003" cy="1857374"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -920,7 +932,15 @@
                 <a:srgbClr val="002060"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>	Maximum Salary Amount In LE</a:t>
+            <a:t>	Maximum Salary Amount In LE       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>RED</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -956,7 +976,15 @@
                 <a:srgbClr val="002060"/>
               </a:solidFill>
             </a:rPr>
-            <a:t> in LE</a:t>
+            <a:t> in LE        </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Yellow</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -12788,19 +12816,19 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.28515625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="14" style="22" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="25" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" style="26" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="26" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="26" customWidth="1"/>
+    <col min="14" max="14" width="2.28515625" style="26" customWidth="1"/>
     <col min="15" max="15" width="8.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17.5703125" style="4" customWidth="1"/>
     <col min="17" max="16384" width="9" style="4"/>
@@ -12870,23 +12898,23 @@
       <c r="E2" s="5">
         <v>31</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="54">
         <f>D2*$E$2</f>
         <v>20816.385920000001</v>
       </c>
-      <c r="G2" s="5">
-        <f>ROUND(F2,0)</f>
+      <c r="G2" s="54">
+        <f t="shared" ref="G2:G11" si="0">ROUND(F2,0)</f>
         <v>20816</v>
       </c>
-      <c r="H2" s="5" cm="1">
-        <f t="array" ref="H2:H11">_xlfn._xlws.SORT(G2:G11,,-1)</f>
-        <v>29688</v>
-      </c>
-      <c r="I2" s="5">
-        <f>IF(H2&gt;20000,H2,"Low Salary")</f>
-        <v>29688</v>
-      </c>
-      <c r="J2" s="8" t="str">
+      <c r="H2" s="5">
+        <f>RANK(F2,F2:F11,0)</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <f>IF(F2&gt;20000,"High Salary","Low Salary")</f>
+        <v>High Salary</v>
+      </c>
+      <c r="J2" s="5" t="str">
         <f>B2 &amp; " " &amp; C2</f>
         <v>Ahmed Yassin</v>
       </c>
@@ -12894,20 +12922,20 @@
         <f>LEN(SUBSTITUTE(J2," ",""))</f>
         <v>11</v>
       </c>
-      <c r="L2" s="9" t="str">
+      <c r="L2" s="8" t="str">
         <f>LEFT(J2,1)</f>
         <v>A</v>
       </c>
-      <c r="M2" s="10" t="str">
+      <c r="M2" s="9" t="str">
         <f>RIGHT(J2,1)</f>
         <v>n</v>
       </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="12">
+      <c r="N2" s="10"/>
+      <c r="O2" s="11">
         <v>1006</v>
       </c>
-      <c r="P2" s="12" t="str">
-        <f>VLOOKUP(O2,'Vlookup sheet'!A1:B15,2,FALSE)</f>
+      <c r="P2" s="11" t="str">
+        <f>VLOOKUP(O2,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
         <v>Mazen Sameh</v>
       </c>
     </row>
@@ -12927,43 +12955,44 @@
       <c r="E3" s="5">
         <v>40</v>
       </c>
-      <c r="F3" s="5">
-        <f>D3*$E$2</f>
+      <c r="F3" s="54">
+        <f t="shared" ref="F3:F11" si="1">D3*$E$2</f>
         <v>25730</v>
       </c>
-      <c r="G3" s="5">
-        <f>ROUND(F3,0)</f>
+      <c r="G3" s="54">
+        <f t="shared" si="0"/>
         <v>25730</v>
       </c>
       <c r="H3" s="5">
-        <v>29459</v>
-      </c>
-      <c r="I3" s="5">
-        <f t="shared" ref="I3:I11" si="0">IF(H3&gt;20000,H3,"Low Salary")</f>
-        <v>29459</v>
-      </c>
-      <c r="J3" s="8" t="str">
-        <f t="shared" ref="J3:J11" si="1">B3 &amp; " " &amp; C3</f>
+        <f t="shared" ref="H3:H11" si="2">RANK(F3,F3:F12,0)</f>
+        <v>5</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <f t="shared" ref="I3:I11" si="3">IF(F3&gt;20000,"High Salary","Low Salary")</f>
+        <v>High Salary</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <f t="shared" ref="J3:J11" si="4">B3 &amp; " " &amp; C3</f>
         <v>Mohamed ismail</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K11" si="2">LEN(SUBSTITUTE(J3," ",""))</f>
+        <f t="shared" ref="K3:K11" si="5">LEN(SUBSTITUTE(J3," ",""))</f>
         <v>13</v>
       </c>
-      <c r="L3" s="9" t="str">
-        <f t="shared" ref="L3:L11" si="3">LEFT(J3,1)</f>
+      <c r="L3" s="8" t="str">
+        <f t="shared" ref="L3:L11" si="6">LEFT(J3,1)</f>
         <v>M</v>
       </c>
-      <c r="M3" s="10" t="str">
-        <f t="shared" ref="M3:M11" si="4">RIGHT(J3,1)</f>
+      <c r="M3" s="9" t="str">
+        <f t="shared" ref="M3:M11" si="7">RIGHT(J3,1)</f>
         <v>l</v>
       </c>
-      <c r="N3" s="11"/>
-      <c r="O3" s="12">
+      <c r="N3" s="10"/>
+      <c r="O3" s="11">
         <v>1008</v>
       </c>
-      <c r="P3" s="12" t="str">
-        <f>VLOOKUP(O3,'Vlookup sheet'!A2:B16,2,FALSE)</f>
+      <c r="P3" s="11" t="str">
+        <f>VLOOKUP(O3,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
         <v>eamy hassan</v>
       </c>
     </row>
@@ -12983,43 +13012,44 @@
       <c r="E4" s="5">
         <v>41</v>
       </c>
-      <c r="F4" s="5">
-        <f>D4*$E$2</f>
+      <c r="F4" s="54">
+        <f t="shared" si="1"/>
         <v>27472.402740000001</v>
       </c>
-      <c r="G4" s="5">
-        <f>ROUND(F4,0)</f>
+      <c r="G4" s="54">
+        <f t="shared" si="0"/>
         <v>27472</v>
       </c>
       <c r="H4" s="5">
-        <v>28888</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>28888</v>
-      </c>
-      <c r="J4" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>High Salary</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Kamal Hussien</v>
       </c>
       <c r="K4" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="L4" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L4" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
-      <c r="M4" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M4" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>n</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="12">
+      <c r="N4" s="10"/>
+      <c r="O4" s="11">
         <v>1013</v>
       </c>
-      <c r="P4" s="12" t="str">
-        <f>VLOOKUP(O4,'Vlookup sheet'!A3:B17,2,FALSE)</f>
+      <c r="P4" s="11" t="str">
+        <f>VLOOKUP(O4,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
         <v>maha ahmed</v>
       </c>
     </row>
@@ -13039,43 +13069,45 @@
       <c r="E5" s="5">
         <v>42</v>
       </c>
-      <c r="F5" s="5">
-        <f>D5*$E$2</f>
+      <c r="F5" s="54">
+        <f t="shared" si="1"/>
         <v>29458.908470000002</v>
       </c>
-      <c r="G5" s="5">
-        <f>ROUND(F5,0)</f>
+      <c r="G5" s="54">
+        <f t="shared" si="0"/>
         <v>29459</v>
       </c>
       <c r="H5" s="5">
-        <v>27472</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" si="0"/>
-        <v>27472</v>
-      </c>
-      <c r="J5" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I5" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>High Salary</v>
+      </c>
+      <c r="J5" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Ali Ismail</v>
       </c>
       <c r="K5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="L5" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L5" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>A</v>
       </c>
-      <c r="M5" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M5" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>l</v>
       </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="12">
+      <c r="N5" s="10"/>
+      <c r="O5" s="11">
         <v>1002</v>
       </c>
-      <c r="P5" s="12" t="s">
-        <v>33</v>
+      <c r="P5" s="11" t="str">
+        <f>VLOOKUP(O5,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
+        <v>mohamed ismail</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -13094,43 +13126,44 @@
       <c r="E6" s="5">
         <v>30.89</v>
       </c>
-      <c r="F6" s="5">
-        <f>D6*$E$2</f>
+      <c r="F6" s="54">
+        <f t="shared" si="1"/>
         <v>17326.94067</v>
       </c>
-      <c r="G6" s="5">
-        <f>ROUND(F6,0)</f>
+      <c r="G6" s="54">
+        <f t="shared" si="0"/>
         <v>17327</v>
       </c>
       <c r="H6" s="5">
-        <v>25730</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>25730</v>
-      </c>
-      <c r="J6" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I6" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Low Salary</v>
+      </c>
+      <c r="J6" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Eyad Ahmed</v>
       </c>
       <c r="K6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="L6" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L6" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>E</v>
       </c>
-      <c r="M6" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M6" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>d</v>
       </c>
-      <c r="N6" s="11"/>
-      <c r="O6" s="12">
+      <c r="N6" s="10"/>
+      <c r="O6" s="11">
         <v>1011</v>
       </c>
-      <c r="P6" s="12" t="str">
-        <f>VLOOKUP(O6,'Vlookup sheet'!A5:B19,2,FALSE)</f>
+      <c r="P6" s="11" t="str">
+        <f>VLOOKUP(O6,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
         <v>ahmed fawzy</v>
       </c>
     </row>
@@ -13150,43 +13183,45 @@
       <c r="E7" s="5">
         <v>49</v>
       </c>
-      <c r="F7" s="5">
-        <f>D7*$E$2</f>
+      <c r="F7" s="54">
+        <f t="shared" si="1"/>
         <v>15500</v>
       </c>
-      <c r="G7" s="5">
-        <f>ROUND(F7,0)</f>
+      <c r="G7" s="54">
+        <f t="shared" si="0"/>
         <v>15500</v>
       </c>
       <c r="H7" s="5">
-        <v>25597</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>25597</v>
-      </c>
-      <c r="J7" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I7" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>Low Salary</v>
+      </c>
+      <c r="J7" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Mazen sameh</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="L7" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L7" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>M</v>
       </c>
-      <c r="M7" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M7" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>h</v>
       </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="12">
+      <c r="N7" s="10"/>
+      <c r="O7" s="11">
         <v>1003</v>
       </c>
-      <c r="P7" s="12" t="s">
-        <v>34</v>
+      <c r="P7" s="11" t="str">
+        <f>VLOOKUP(O7,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
+        <v>kamal Hussien</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -13205,43 +13240,45 @@
       <c r="E8" s="5">
         <v>47</v>
       </c>
-      <c r="F8" s="5">
-        <f>D8*$E$2</f>
+      <c r="F8" s="54">
+        <f t="shared" si="1"/>
         <v>25596.908939999998</v>
       </c>
-      <c r="G8" s="5">
-        <f>ROUND(F8,0)</f>
+      <c r="G8" s="54">
+        <f t="shared" si="0"/>
         <v>25597</v>
       </c>
       <c r="H8" s="5">
-        <v>20816</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>20816</v>
-      </c>
-      <c r="J8" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>High Salary</v>
+      </c>
+      <c r="J8" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Nermeen Ali</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="L8" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L8" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>N</v>
       </c>
-      <c r="M8" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M8" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>i</v>
       </c>
-      <c r="N8" s="11"/>
-      <c r="O8" s="12">
+      <c r="N8" s="10"/>
+      <c r="O8" s="11">
         <v>1005</v>
       </c>
-      <c r="P8" s="12" t="s">
-        <v>38</v>
+      <c r="P8" s="11" t="str">
+        <f>VLOOKUP(O8,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
+        <v>eyad ahmed</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -13260,43 +13297,44 @@
       <c r="E9" s="5">
         <v>30.89</v>
       </c>
-      <c r="F9" s="5">
-        <f>D9*$E$2</f>
+      <c r="F9" s="54">
+        <f t="shared" si="1"/>
         <v>28887.518640000002</v>
       </c>
-      <c r="G9" s="5">
-        <f>ROUND(F9,0)</f>
+      <c r="G9" s="54">
+        <f t="shared" si="0"/>
         <v>28888</v>
       </c>
       <c r="H9" s="5">
-        <v>17593</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Low Salary</v>
-      </c>
-      <c r="J9" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
+        <v>High Salary</v>
+      </c>
+      <c r="J9" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Ramy Hassan</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="L9" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L9" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>R</v>
       </c>
-      <c r="M9" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M9" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>n</v>
       </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="12">
+      <c r="N9" s="10"/>
+      <c r="O9" s="11">
         <v>1010</v>
       </c>
-      <c r="P9" s="12" t="str">
-        <f>VLOOKUP(O9,'Vlookup sheet'!A8:B22,2,FALSE)</f>
+      <c r="P9" s="11" t="str">
+        <f>VLOOKUP(O9,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
         <v>yamen mohamed</v>
       </c>
     </row>
@@ -13316,43 +13354,45 @@
       <c r="E10" s="5">
         <v>30.89</v>
       </c>
-      <c r="F10" s="5">
-        <f>D10*$E$2</f>
+      <c r="F10" s="54">
+        <f t="shared" si="1"/>
         <v>17593.358080000002</v>
       </c>
-      <c r="G10" s="5">
-        <f>ROUND(F10,0)</f>
+      <c r="G10" s="54">
+        <f t="shared" si="0"/>
         <v>17593</v>
       </c>
       <c r="H10" s="5">
-        <v>17327</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="I10" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Low Salary</v>
       </c>
-      <c r="J10" s="8" t="str">
-        <f t="shared" si="1"/>
+      <c r="J10" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Hassan Sayed</v>
       </c>
       <c r="K10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="L10" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L10" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>H</v>
       </c>
-      <c r="M10" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M10" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>d</v>
       </c>
-      <c r="N10" s="11"/>
-      <c r="O10" s="12">
+      <c r="N10" s="10"/>
+      <c r="O10" s="11">
         <v>1006</v>
       </c>
-      <c r="P10" s="12" t="s">
-        <v>40</v>
+      <c r="P10" s="11" t="str">
+        <f>VLOOKUP(O10,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
+        <v>Mazen Sameh</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -13371,237 +13411,239 @@
       <c r="E11" s="5">
         <v>30.89</v>
       </c>
-      <c r="F11" s="5">
-        <f>D11*$E$2</f>
+      <c r="F11" s="54">
+        <f t="shared" si="1"/>
         <v>29688.218259999998</v>
       </c>
-      <c r="G11" s="5">
-        <f>ROUND(F11,0)</f>
+      <c r="G11" s="54">
+        <f t="shared" si="0"/>
         <v>29688</v>
       </c>
       <c r="H11" s="5">
-        <v>15500</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="I11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Low Salary</v>
-      </c>
-      <c r="J11" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
+        <v>High Salary</v>
+      </c>
+      <c r="J11" s="5" t="str">
+        <f t="shared" si="4"/>
         <v>Yamen Mohamed</v>
       </c>
       <c r="K11" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="L11" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="L11" s="8" t="str">
+        <f t="shared" si="6"/>
         <v>Y</v>
       </c>
-      <c r="M11" s="10" t="str">
-        <f t="shared" si="4"/>
+      <c r="M11" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>d</v>
       </c>
-      <c r="N11" s="11"/>
-      <c r="O11" s="12">
+      <c r="N11" s="10"/>
+      <c r="O11" s="11">
         <v>1004</v>
       </c>
-      <c r="P11" s="12" t="s">
-        <v>36</v>
+      <c r="P11" s="11" t="str">
+        <f>VLOOKUP(O11,'Vlookup sheet'!$A$1:$B$15,2,FALSE)</f>
+        <v>ali ismail</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" thickBot="1">
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="52">
+      <c r="D13" s="24"/>
+      <c r="E13" s="46">
         <f>SUM(G2:G11)</f>
         <v>238070</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" thickBot="1">
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="53">
+      <c r="D14" s="28"/>
+      <c r="E14" s="47">
         <f>AVERAGE(G2:G11)</f>
         <v>23807</v>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="29"/>
     </row>
     <row r="15" spans="1:16" ht="15.75" thickBot="1">
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="53">
+      <c r="D15" s="28"/>
+      <c r="E15" s="47">
         <f>MAX(G2:G11)</f>
         <v>29688</v>
       </c>
-      <c r="M15" s="31"/>
+      <c r="M15" s="30"/>
     </row>
     <row r="16" spans="1:16" ht="15.75" thickBot="1">
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="53">
+      <c r="D16" s="28"/>
+      <c r="E16" s="47">
         <f>MIN(G2:G11)</f>
         <v>15500</v>
       </c>
-      <c r="M16" s="31"/>
+      <c r="M16" s="30"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1">
       <c r="B17" s="3"/>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="53">
+      <c r="D17" s="28"/>
+      <c r="E17" s="47">
         <f>COUNT(G2:G11)</f>
         <v>10</v>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="53">
+      <c r="D18" s="28"/>
+      <c r="E18" s="47">
         <f>COUNTA(J2:J11)</f>
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="53">
-        <f>COUNTA(B2:B11)</f>
-        <v>10</v>
+      <c r="D19" s="28"/>
+      <c r="E19" s="47">
+        <f>COUNTBLANK(B2:B11)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="53">
-        <f>LARGE(H2:H11,2)</f>
-        <v>29459</v>
+      <c r="D20" s="28"/>
+      <c r="E20" s="47">
+        <f>LARGE(F2:F11,2)</f>
+        <v>29458.908470000002</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="54">
-        <f>SMALL(H2:H11,2)</f>
-        <v>17327</v>
+      <c r="D21" s="33"/>
+      <c r="E21" s="48">
+        <f>SMALL(F2:F11,2)</f>
+        <v>17326.94067</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="54">
-        <f>SUMIF(H2:H11,"&gt;20000")</f>
-        <v>187650</v>
+      <c r="D22" s="33"/>
+      <c r="E22" s="48">
+        <f>SUMIF(I2:I11,"High Salary",F2:F11)</f>
+        <v>187650.34297</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="54">
-        <f>COUNTIF(H2:H11,"&gt;20000")</f>
+      <c r="D23" s="33"/>
+      <c r="E23" s="48">
+        <f>COUNTIF(F2:F11,"&gt;20000")</f>
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="23.25">
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
     </row>
     <row r="28" spans="2:7" ht="18.75">
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="51"/>
     </row>
     <row r="29" spans="2:7" ht="18.75">
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="2:7" ht="18.75">
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="47"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="2:7" ht="18.75">
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51"/>
     </row>
     <row r="32" spans="2:7" ht="18.75">
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="51"/>
     </row>
     <row r="33" spans="3:6" ht="18.75">
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="51"/>
     </row>
     <row r="36" spans="3:6">
-      <c r="F36" s="35"/>
+      <c r="F36" s="34"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M11">
@@ -13616,6 +13658,10 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D30:F30"/>
   </mergeCells>
+  <conditionalFormatting sqref="F1:F11">
+    <cfRule type="top10" dxfId="0" priority="2" rank="1"/>
+    <cfRule type="top10" dxfId="1" priority="1" percent="1" bottom="1" rank="1"/>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C26" r:id="rId1" xr:uid="{9B35966A-EBE3-463F-89A3-32D052E9D6F3}"/>
   </hyperlinks>
@@ -13635,122 +13681,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" thickBot="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="38">
+      <c r="A2" s="37">
         <v>1001</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="38" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="40">
+      <c r="A3" s="39">
         <v>1002</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="42">
+      <c r="A4" s="41">
         <v>1003</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="40">
+      <c r="A5" s="39">
         <v>1004</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="42">
+      <c r="A6" s="41">
         <v>1005</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="42" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="40">
+      <c r="A7" s="39">
         <v>1006</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="40" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="42">
+      <c r="A8" s="41">
         <v>1007</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="42" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="40">
+      <c r="A9" s="39">
         <v>1008</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="42">
+      <c r="A10" s="41">
         <v>1009</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="40">
+      <c r="A11" s="39">
         <v>1010</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="42">
+      <c r="A12" s="41">
         <v>1011</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="42" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="40">
+      <c r="A13" s="39">
         <v>1012</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="40" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="42">
+      <c r="A14" s="41">
         <v>1013</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="42" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="44">
+      <c r="A15" s="43">
         <v>1014</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="44" t="s">
         <v>50</v>
       </c>
     </row>
